--- a/cases/Case_14bus_v3/pf_info_extendedCase_14bus_v3.xlsx
+++ b/cases/Case_14bus_v3/pf_info_extendedCase_14bus_v3.xlsx
@@ -555,10 +555,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.30169865804515</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.2720761285389708</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -578,10 +578,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.3999998687949716</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4923645571544422</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.3999999964536085</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2009839812538434</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -624,10 +624,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>-7.337447105459916E-08</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-6.815909955881772E-08</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -647,10 +647,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2.080618936861622E-08</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4.806437912951989E-08</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.300000011614257</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.8385541716135918</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>9.210298135275963E-09</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2.441587554358193E-08</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -716,10 +716,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.3500000070386378</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.2260144251308303</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>-9.346296125922748E-09</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-5.64193597674123E-08</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -762,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.2000000044083893</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>5.992976739865874E-10</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.02499998911516299</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>-1.193570786650611E-08</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -808,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.02499999956651383</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-3.396017703161114E-09</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -831,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.09999996142565637</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>-3.674451959367886E-08</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.129059021412628</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>-1.195166560163941E-08</v>
       </c>
     </row>
     <row r="16" spans="1:7">
